--- a/experiment_results/wu_calibration/rtt_bursts_rps10_att4_WU500000.xlsx
+++ b/experiment_results/wu_calibration/rtt_bursts_rps10_att4_WU500000.xlsx
@@ -481,17 +481,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>278</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -533,22 +533,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:016.4</t>
+          <t>00:016.6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>171.4</t>
+          <t>210.1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>385.4</t>
+          <t>453.6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>92.74</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>74048</t>
+          <t>91833</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -590,17 +590,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:023.3</t>
+          <t>00:023.0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>899.9</t>
+          <t>1028.3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>513.8</t>
+          <t>542.9</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>157925</t>
+          <t>190845</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -647,27 +647,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:053.7</t>
+          <t>00:054.7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1081.8</t>
+          <t>1287.9</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>487.9</t>
+          <t>451.6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>176927</t>
+          <t>246275</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -704,22 +704,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:053.7</t>
+          <t>00:054.7</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1081.8</t>
+          <t>1287.9</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>487.9</t>
+          <t>451.6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>195929</t>
+          <t>301705</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -761,27 +761,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01:016.5</t>
+          <t>01:016.8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1180.6</t>
+          <t>1198.9</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>404.9</t>
+          <t>464.1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>232873</t>
+          <t>320437</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -818,22 +818,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:016.5</t>
+          <t>01:016.8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1180.6</t>
+          <t>1198.9</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>404.9</t>
+          <t>464.1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>269816</t>
+          <t>339169</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
